--- a/Excel/Enterprises/Enterprise_CroppingGrains_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_CroppingGrains_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82A046B-1AF0-4B58-8EFC-90D3F98E537B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED2FBB6-2A0D-4694-A12A-D71EE9F30E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2055" yWindow="1140" windowWidth="34845" windowHeight="17985" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="2325" yWindow="360" windowWidth="36060" windowHeight="19710" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -4346,6 +4346,8 @@
           <c:showLeaderLines val="1"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
+        <c:splitType val="percent"/>
+        <c:splitPos val="10"/>
         <c:secondPieSize val="75"/>
         <c:serLines>
           <c:spPr>
@@ -4574,6 +4576,8 @@
           <c:showLeaderLines val="1"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
+        <c:splitType val="percent"/>
+        <c:splitPos val="10"/>
         <c:secondPieSize val="75"/>
         <c:serLines>
           <c:spPr>
@@ -13738,11 +13742,11 @@
         <v>8</v>
       </c>
       <c r="H40" s="1" t="e">
-        <f t="shared" ref="H40:I47" si="2">E40</f>
+        <f t="shared" ref="H40:H47" si="2">E40</f>
         <v>#NAME?</v>
       </c>
       <c r="I40" s="1" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I40:I50" si="3">F40</f>
         <v>#NAME?</v>
       </c>
       <c r="J40" s="10" t="s">
@@ -13769,7 +13773,7 @@
         <v>#NAME?</v>
       </c>
       <c r="I41" s="1" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#NAME?</v>
       </c>
       <c r="J41" s="10" t="s">
@@ -13796,7 +13800,7 @@
         <v>#NAME?</v>
       </c>
       <c r="I42" s="1" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#NAME?</v>
       </c>
       <c r="J42" s="10" t="s">
@@ -13823,7 +13827,7 @@
         <v>#NAME?</v>
       </c>
       <c r="I43" s="1" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#NAME?</v>
       </c>
       <c r="J43" s="10" t="s">
@@ -13850,7 +13854,7 @@
         <v>#NAME?</v>
       </c>
       <c r="I44" s="1" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#NAME?</v>
       </c>
       <c r="J44" s="10" t="s">
@@ -13877,7 +13881,7 @@
         <v>#NAME?</v>
       </c>
       <c r="I45" s="1" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#NAME?</v>
       </c>
       <c r="J45" s="10" t="s">
@@ -13904,7 +13908,7 @@
         <v>#NAME?</v>
       </c>
       <c r="I46" s="1" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#NAME?</v>
       </c>
       <c r="J46" s="10" t="s">
@@ -13932,7 +13936,7 @@
         <v>#NAME?</v>
       </c>
       <c r="I47" s="1" t="e">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>#NAME?</v>
       </c>
       <c r="J47" s="10" t="s">
@@ -13959,7 +13963,7 @@
         <v>#NAME?</v>
       </c>
       <c r="I48" s="1" t="e">
-        <f>F48</f>
+        <f t="shared" si="3"/>
         <v>#NAME?</v>
       </c>
       <c r="J48" s="10" t="s">
@@ -13982,7 +13986,7 @@
         <v>8</v>
       </c>
       <c r="H49" s="1" t="e">
-        <f t="shared" ref="H49:I50" si="3">E49</f>
+        <f t="shared" ref="H49:H50" si="4">E49</f>
         <v>#NAME?</v>
       </c>
       <c r="I49" s="1" t="e">
@@ -14009,7 +14013,7 @@
         <v>8</v>
       </c>
       <c r="H50" s="1" t="e">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>#NAME?</v>
       </c>
       <c r="I50" s="1" t="e">
@@ -15931,11 +15935,11 @@
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
       <c r="E79" s="77" t="str">
-        <f t="shared" ref="E79:F79" si="0">IF(ISBLANK($D79), 0, IF(ISNUMBER(SEARCH("reporting", $D79)), E55-$E$67, "Enter value"))</f>
+        <f>IF(ISBLANK($D79), 0, IF(ISNUMBER(SEARCH("reporting", $D79)), E55-$E$68, "Enter value"))</f>
         <v>Enter value</v>
       </c>
       <c r="F79" s="77" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK($D79), 0, IF(ISNUMBER(SEARCH("reporting", $D79)), F55-$E$68, "Enter value"))</f>
         <v>Enter value</v>
       </c>
       <c r="G79" s="10" t="s">
@@ -15944,11 +15948,11 @@
     </row>
     <row r="80" spans="4:7" x14ac:dyDescent="0.25">
       <c r="E80" s="77">
-        <f t="shared" ref="E80:F80" si="1">IF(ISBLANK($D80), 0, IF(ISNUMBER(SEARCH("reporting", $D80)), E56-$E$67, "Enter value"))</f>
+        <f>IF(ISBLANK($D80), 0, IF(ISNUMBER(SEARCH("reporting", $D80)), E56-$E$69, "Enter value"))</f>
         <v>0</v>
       </c>
       <c r="F80" s="77">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK($D80), 0, IF(ISNUMBER(SEARCH("reporting", $D80)), F56-$E$69, "Enter value"))</f>
         <v>0</v>
       </c>
       <c r="G80" s="10" t="s">
@@ -15957,11 +15961,11 @@
     </row>
     <row r="81" spans="4:7" x14ac:dyDescent="0.25">
       <c r="E81" s="77">
-        <f t="shared" ref="E81:F81" si="2">IF(ISBLANK($D81), 0, IF(ISNUMBER(SEARCH("reporting", $D81)), E57-$E$67, "Enter value"))</f>
+        <f>IF(ISBLANK($D81), 0, IF(ISNUMBER(SEARCH("reporting", $D81)), E57-$E$70, "Enter value"))</f>
         <v>0</v>
       </c>
       <c r="F81" s="77">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK($D81), 0, IF(ISNUMBER(SEARCH("reporting", $D81)), F57-$E$70, "Enter value"))</f>
         <v>0</v>
       </c>
       <c r="G81" s="10" t="s">
@@ -15970,11 +15974,11 @@
     </row>
     <row r="82" spans="4:7" x14ac:dyDescent="0.25">
       <c r="E82" s="77">
-        <f t="shared" ref="E82:F82" si="3">IF(ISBLANK($D82), 0, IF(ISNUMBER(SEARCH("reporting", $D82)), E58-$E$67, "Enter value"))</f>
+        <f>IF(ISBLANK($D82), 0, IF(ISNUMBER(SEARCH("reporting", $D82)), E58-$E$71, "Enter value"))</f>
         <v>0</v>
       </c>
       <c r="F82" s="77">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK($D82), 0, IF(ISNUMBER(SEARCH("reporting", $D82)), F58-$E$71, "Enter value"))</f>
         <v>0</v>
       </c>
       <c r="G82" s="10" t="s">

--- a/Excel/Enterprises/Enterprise_CroppingGrains_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_CroppingGrains_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED2FBB6-2A0D-4694-A12A-D71EE9F30E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0701D42C-1A79-4981-8A06-E3C3CADE530C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2325" yWindow="360" windowWidth="36060" windowHeight="19710" activeTab="4" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="2055" yWindow="1260" windowWidth="36330" windowHeight="19485" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="298">
   <si>
     <t>Home</t>
   </si>
@@ -1271,9 +1271,6 @@
   </si>
   <si>
     <t>Crop management</t>
-  </si>
-  <si>
-    <t>Residue management</t>
   </si>
 </sst>
 </file>
@@ -16164,8 +16161,9 @@
       </c>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="D8" s="1" t="s">
-        <v>150</v>
+      <c r="D8" s="1" t="str">
+        <f>"Grain yield"</f>
+        <v>Grain yield</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>235</v>
@@ -16546,8 +16544,9 @@
       </c>
     </row>
     <row r="33" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D33" s="1" t="s">
-        <v>298</v>
+      <c r="D33" s="1" t="str">
+        <f>"Residue management"</f>
+        <v>Residue management</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>235</v>
@@ -21519,17 +21518,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -21724,11 +21712,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -21737,18 +21732,11 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21767,18 +21755,29 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/Enterprises/Enterprise_CroppingGrains_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_CroppingGrains_Template_WIP_v01.xlsx
@@ -609,9 +609,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -619,9 +619,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>DD/MM/YYYY or DD Month YYYY</t>
@@ -630,9 +630,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -640,9 +640,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Automatically calculated, 12 months after start date</t>
@@ -666,9 +666,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -676,9 +676,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Please select</t>
@@ -1289,108 +1289,106 @@
   </numFmts>
   <fonts count="55" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -1401,219 +1399,217 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <u/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF242424"/>
       <name val="Consolas"/>
       <family val="3"/>
@@ -1621,34 +1617,34 @@
     <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF0C769E"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -2501,11 +2497,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2525,11 +2520,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2549,11 +2543,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2573,11 +2566,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2597,11 +2589,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2621,11 +2612,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2645,11 +2635,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2669,11 +2658,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2693,11 +2681,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2717,11 +2704,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2741,11 +2727,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2765,11 +2750,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2789,11 +2773,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2813,11 +2796,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2837,11 +2819,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2861,11 +2842,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2885,11 +2865,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2909,11 +2888,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2933,11 +2911,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2957,11 +2934,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2981,11 +2957,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3005,11 +2980,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3029,11 +3003,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3053,11 +3026,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3077,11 +3049,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3101,11 +3072,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3125,11 +3095,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3149,11 +3118,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3173,11 +3141,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3197,11 +3164,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3221,11 +3187,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3245,11 +3210,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3269,11 +3233,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3293,11 +3256,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3317,11 +3279,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3341,11 +3302,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3365,11 +3325,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3389,11 +3348,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3413,11 +3371,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3437,11 +3394,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3461,11 +3417,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3775,7 +3730,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4437,7 +4392,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4674,7 +4629,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4811,7 +4766,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -6216,24 +6171,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{6496CA75-FED4-4E21-A81D-BDC20736B7B5}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6297,24 +6252,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{1A778010-8EF6-4986-9F7A-ED1F5F66D6A5}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6378,24 +6333,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{7DC837A9-60D0-4FEE-9D60-F5F33C8747DB}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6459,24 +6414,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A1C4261C-1106-48B4-9C10-E82D60412011}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6540,24 +6495,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{AE965B10-5BD0-44CC-8118-41596A6F15E2}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6621,24 +6576,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{304D704D-8D75-4B25-B661-1CD4BF80A14D}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6701,16 +6656,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -6776,36 +6731,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -6871,18 +6826,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -6950,7 +6905,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -7068,16 +7023,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -7143,36 +7098,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -7238,18 +7193,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7417,16 +7372,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7492,36 +7447,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7587,18 +7542,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7660,7 +7615,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -7684,7 +7639,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7752,7 +7707,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
@@ -7875,16 +7830,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7950,36 +7905,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -8045,18 +8000,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8228,7 +8183,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8252,7 +8207,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8314,7 +8269,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8338,7 +8293,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8400,7 +8355,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8424,7 +8379,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8486,7 +8441,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8510,7 +8465,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8572,7 +8527,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8596,7 +8551,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8658,7 +8613,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8682,7 +8637,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8744,7 +8699,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8768,7 +8723,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8837,24 +8792,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{325659CC-BF18-4027-9C39-6B59F0E2F578}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8918,24 +8873,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A9E71E38-28CF-40B4-A787-CD2A933BF092}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8999,24 +8954,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{FBAAA7CE-3F73-42A7-B887-E644937F7159}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9080,24 +9035,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{E266E2BA-6A96-4903-9E52-5C6BCFEF9FF1}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9161,24 +9116,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{F8F36783-2D83-448C-9BE3-D1653ADA37CE}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9242,24 +9197,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{9792A2EE-0599-40C6-BEC6-FB928C51F2CA}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9323,24 +9278,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{9FBD39D1-A40C-4D41-815F-1614BABEEB25}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9404,24 +9359,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{48E1D669-5050-474F-B029-B219812AC417}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9484,16 +9439,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9559,36 +9514,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9654,18 +9609,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9733,7 +9688,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -9851,16 +9806,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9926,36 +9881,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -10021,18 +9976,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10200,16 +10155,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10275,36 +10230,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10370,18 +10325,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10443,7 +10398,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10467,7 +10422,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10535,7 +10490,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
@@ -10658,16 +10613,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10733,18 +10688,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10916,7 +10871,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10940,7 +10895,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11002,7 +10957,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11026,7 +10981,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11088,7 +11043,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11112,7 +11067,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11174,7 +11129,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11198,7 +11153,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11260,7 +11215,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11284,7 +11239,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11346,7 +11301,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11370,7 +11325,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11432,7 +11387,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11456,7 +11411,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11525,24 +11480,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{B945A79A-D657-45FF-8794-B3F7FE79A7B2}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -11606,24 +11561,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A0887E06-5564-4610-905A-7D5E4A0E50F4}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -11686,7 +11641,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="2000"/>
+            <a:rPr lang="en-AU" sz="1800"/>
             <a:t>Grain sold</a:t>
           </a:r>
         </a:p>
@@ -11823,7 +11778,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="2000"/>
+            <a:rPr lang="en-AU" sz="1800"/>
             <a:t>Baled hay/silage sold</a:t>
           </a:r>
         </a:p>
@@ -12705,12 +12660,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -12921,31 +12876,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="82" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="83" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -12963,7 +12918,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:K87"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" customWidth="1"/>
@@ -12991,7 +12946,7 @@
       <c r="J1" s="93"/>
       <c r="K1" s="93"/>
     </row>
-    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -13003,7 +12958,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -13018,7 +12973,7 @@
       <c r="J3" s="94"/>
       <c r="K3" s="94"/>
     </row>
-    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -13028,10 +12983,10 @@
         <v>Emissions breakdown for activities running between 01 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
@@ -13039,13 +12994,13 @@
         <v>272</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -13070,7 +13025,7 @@
       </c>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1" t="s">
         <v>134</v>
@@ -13098,7 +13053,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -13128,7 +13083,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -13159,7 +13114,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -13190,7 +13145,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -13221,7 +13176,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -13252,7 +13207,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>174</v>
@@ -13280,7 +13235,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -13310,7 +13265,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -13341,7 +13296,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -13372,7 +13327,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -13403,7 +13358,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -13434,7 +13389,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="1" t="s">
         <v>141</v>
       </c>
@@ -13461,7 +13416,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
         <v>143</v>
@@ -13489,7 +13444,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="D23" s="1" t="s">
         <v>144</v>
@@ -13517,7 +13472,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="D24" s="1" t="s">
         <v>145</v>
@@ -13545,7 +13500,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
         <v>146</v>
       </c>
@@ -13572,7 +13527,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="1" t="s">
         <v>147</v>
       </c>
@@ -13599,7 +13554,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="88" t="s">
         <v>5</v>
       </c>
@@ -13618,15 +13573,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="80" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D32" s="12" t="s">
         <v>274</v>
       </c>
@@ -13647,7 +13602,7 @@
       </c>
       <c r="J32" s="12"/>
     </row>
-    <row r="33" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="1" t="e" cm="1">
         <f t="array" ref="D33">"14.1.1-2 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
         <v>#NAME?</v>
@@ -13675,7 +13630,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="34" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="88" t="s">
         <v>275</v>
       </c>
@@ -13694,15 +13649,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="80" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="12" t="s">
         <v>277</v>
       </c>
@@ -13723,7 +13678,7 @@
       </c>
       <c r="J39" s="12"/>
     </row>
-    <row r="40" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="s">
         <v>278</v>
       </c>
@@ -13750,7 +13705,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="1" t="s">
         <v>279</v>
       </c>
@@ -13777,7 +13732,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="1" t="s">
         <v>280</v>
       </c>
@@ -13804,7 +13759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="1" t="s">
         <v>281</v>
       </c>
@@ -13831,7 +13786,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="1" t="s">
         <v>282</v>
       </c>
@@ -13858,7 +13813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="1" t="s">
         <v>283</v>
       </c>
@@ -13885,7 +13840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="1" t="s">
         <v>284</v>
       </c>
@@ -13912,7 +13867,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="47" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="1" t="e" cm="1">
         <f t="array" ref="D47">"15.12.1.1 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
         <v>#NAME?</v>
@@ -13940,7 +13895,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="1" t="s">
         <v>285</v>
       </c>
@@ -13967,7 +13922,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="1" t="s">
         <v>286</v>
       </c>
@@ -13994,7 +13949,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="1" t="s">
         <v>287</v>
       </c>
@@ -14021,7 +13976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="88" t="s">
         <v>288</v>
       </c>
@@ -14040,16 +13995,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D54" s="80" t="str">
         <f>"Carbon removals from plantings for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Carbon removals from plantings for the activity period 1 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="55" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="88" t="s">
         <v>289</v>
       </c>
@@ -14061,16 +14016,16 @@
         <v>128</v>
       </c>
     </row>
-    <row r="57" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="80" t="str">
         <f>"Net emissions for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Net emissions for the activity period 1 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="60" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="12"/>
       <c r="E61" s="12" t="s">
         <v>131</v>
@@ -14080,7 +14035,7 @@
       </c>
       <c r="G61" s="12"/>
     </row>
-    <row r="62" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="97" t="s">
         <v>290</v>
       </c>
@@ -14096,7 +14051,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="63" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="97" t="s">
         <v>292</v>
       </c>
@@ -14112,30 +14067,30 @@
         <v>291</v>
       </c>
     </row>
-    <row r="64" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -14149,7 +14104,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:N58"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -14159,7 +14114,7 @@
     <col min="14" max="14" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="93" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" s="93" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="A1" s="11" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -14167,8 +14122,8 @@
         <v>295</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C3" s="94"/>
       <c r="D3" s="94"/>
       <c r="E3" s="94"/>
@@ -14182,13 +14137,13 @@
       <c r="M3" s="94"/>
       <c r="N3" s="94"/>
     </row>
-    <row r="32" spans="4:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:4" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D32" s="2" t="str">
         <f>"Emissions for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Emissions for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D35" s="12"/>
       <c r="E35" s="12" t="s">
         <v>131</v>
@@ -14198,7 +14153,7 @@
       </c>
       <c r="G35" s="12"/>
     </row>
-    <row r="36" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D36" s="78" t="s">
         <v>293</v>
       </c>
@@ -14214,7 +14169,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D37" s="78" t="s">
         <v>294</v>
       </c>
@@ -14230,18 +14185,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D39" s="2" t="str">
         <f>"Product emissions intensity for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Product emissions intensity for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="42" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D42" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="43" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D43" s="12" t="s">
         <v>133</v>
       </c>
@@ -14264,7 +14219,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D44" s="1" t="s">
         <v>169</v>
       </c>
@@ -14291,7 +14246,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="45" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D45" s="1" t="s">
         <v>170</v>
       </c>
@@ -14318,7 +14273,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="46" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D46" s="1" t="s">
         <v>159</v>
       </c>
@@ -14340,7 +14295,7 @@
       </c>
       <c r="J46" s="10"/>
     </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D47" s="1" t="s">
         <v>171</v>
       </c>
@@ -14367,7 +14322,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="1" t="s">
         <v>172</v>
       </c>
@@ -14394,7 +14349,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="49" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D49" s="1" t="s">
         <v>160</v>
       </c>
@@ -14416,12 +14371,12 @@
       </c>
       <c r="J49" s="10"/>
     </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="52" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D52" s="12" t="s">
         <v>133</v>
       </c>
@@ -14444,7 +14399,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D53" s="1" t="s">
         <v>169</v>
       </c>
@@ -14471,7 +14426,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="54" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="1" t="s">
         <v>170</v>
       </c>
@@ -14498,7 +14453,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="55" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D55" s="1" t="s">
         <v>159</v>
       </c>
@@ -14520,7 +14475,7 @@
       </c>
       <c r="J55" s="10"/>
     </row>
-    <row r="56" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D56" s="1" t="s">
         <v>171</v>
       </c>
@@ -14547,7 +14502,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D57" s="1" t="s">
         <v>172</v>
       </c>
@@ -14574,7 +14529,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D58" s="1" t="s">
         <v>160</v>
       </c>
@@ -14609,7 +14564,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:AA115"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" style="23" customWidth="1"/>
@@ -14630,7 +14585,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="23" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="23" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -14641,7 +14596,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -14668,7 +14623,7 @@
       <c r="W3" s="25"/>
       <c r="X3" s="25"/>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -14683,19 +14638,19 @@
       <c r="J4" s="31"/>
       <c r="K4" s="31"/>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
         <v>96</v>
       </c>
       <c r="N5" s="32"/>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="34"/>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -14707,7 +14662,7 @@
       <c r="F7" s="45"/>
       <c r="G7" s="46"/>
     </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -14719,14 +14674,14 @@
       <c r="F8" s="48"/>
       <c r="G8" s="49"/>
     </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1"/>
       <c r="E9" s="50"/>
       <c r="F9" s="17"/>
       <c r="N9" s="36"/>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -14741,7 +14696,7 @@
       </c>
       <c r="N10" s="36"/>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -14758,7 +14713,7 @@
       <c r="G11" s="1"/>
       <c r="N11" s="41"/>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -14773,7 +14728,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -14790,7 +14745,7 @@
       <c r="N13" s="43"/>
       <c r="O13" s="43"/>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -14807,7 +14762,7 @@
       <c r="N14" s="43"/>
       <c r="O14" s="43"/>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>109</v>
@@ -14821,7 +14776,7 @@
       <c r="N15" s="43"/>
       <c r="O15" s="43"/>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -14837,7 +14792,7 @@
       <c r="N16" s="43"/>
       <c r="O16" s="43"/>
     </row>
-    <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -14852,7 +14807,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -14866,7 +14821,7 @@
       </c>
       <c r="F18" s="17"/>
     </row>
-    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -14881,7 +14836,7 @@
       <c r="G19" s="51"/>
       <c r="N19" s="32"/>
     </row>
-    <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -14897,7 +14852,7 @@
       <c r="G20" s="50"/>
       <c r="N20" s="34"/>
     </row>
-    <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="1" t="s">
         <v>115</v>
@@ -14909,7 +14864,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="50"/>
     </row>
-    <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
         <v>69</v>
@@ -14920,29 +14875,29 @@
       </c>
       <c r="G22" s="54"/>
     </row>
-    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="N25" s="34"/>
     </row>
-    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="L30" s="52"/>
       <c r="M30" s="52"/>
@@ -14959,7 +14914,7 @@
       <c r="X30" s="52"/>
       <c r="Y30" s="52"/>
     </row>
-    <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
       <c r="L31" s="53"/>
       <c r="M31" s="53"/>
@@ -14976,7 +14931,7 @@
       <c r="X31" s="53"/>
       <c r="Y31" s="53"/>
     </row>
-    <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
       <c r="L32" s="53"/>
       <c r="M32" s="53"/>
@@ -14993,7 +14948,7 @@
       <c r="X32" s="53"/>
       <c r="Y32" s="53"/>
     </row>
-    <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
       <c r="L33" s="53"/>
       <c r="M33" s="53"/>
@@ -15010,7 +14965,7 @@
       <c r="X33" s="53"/>
       <c r="Y33" s="53"/>
     </row>
-    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="J34" s="55"/>
       <c r="K34" s="56"/>
@@ -15029,7 +14984,7 @@
       <c r="X34" s="53"/>
       <c r="Y34" s="53"/>
     </row>
-    <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="J35" s="55"/>
       <c r="K35" s="56"/>
@@ -15048,7 +15003,7 @@
       <c r="X35" s="53"/>
       <c r="Y35" s="53"/>
     </row>
-    <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="57"/>
       <c r="E36" s="57"/>
@@ -15073,7 +15028,7 @@
       <c r="X36" s="53"/>
       <c r="Y36" s="53"/>
     </row>
-    <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="57"/>
       <c r="E37" s="57"/>
@@ -15098,7 +15053,7 @@
       <c r="X37" s="53"/>
       <c r="Y37" s="53"/>
     </row>
-    <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="57"/>
       <c r="E38" s="57"/>
@@ -15123,7 +15078,7 @@
       <c r="X38" s="53"/>
       <c r="Y38" s="53"/>
     </row>
-    <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="57"/>
       <c r="E39" s="57"/>
@@ -15148,7 +15103,7 @@
       <c r="X39" s="53"/>
       <c r="Y39" s="53"/>
     </row>
-    <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="60"/>
       <c r="E40" s="60"/>
@@ -15173,104 +15128,104 @@
       <c r="X40" s="63"/>
       <c r="Y40" s="63"/>
     </row>
-    <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="64"/>
       <c r="E47" s="64"/>
       <c r="F47" s="64"/>
       <c r="G47" s="64"/>
       <c r="H47" s="64"/>
     </row>
-    <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="65"/>
       <c r="E48" s="65"/>
       <c r="F48" s="66"/>
       <c r="G48" s="66"/>
       <c r="H48" s="65"/>
     </row>
-    <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="65"/>
       <c r="E49" s="65"/>
       <c r="F49" s="66"/>
       <c r="G49" s="66"/>
       <c r="H49" s="65"/>
     </row>
-    <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="65"/>
       <c r="E50" s="65"/>
       <c r="F50" s="66"/>
       <c r="G50" s="66"/>
       <c r="H50" s="65"/>
     </row>
-    <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="67"/>
       <c r="E51" s="68"/>
       <c r="F51" s="68"/>
       <c r="G51" s="68"/>
       <c r="H51" s="69"/>
     </row>
-    <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G54" s="70"/>
     </row>
-    <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="71"/>
       <c r="F57" s="72"/>
     </row>
-    <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="1"/>
       <c r="E58" s="73"/>
     </row>
-    <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="1"/>
       <c r="E59" s="73"/>
     </row>
-    <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="1"/>
       <c r="E60" s="74"/>
     </row>
-    <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="1"/>
     </row>
-    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="71"/>
     </row>
-    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="1"/>
       <c r="E64" s="73"/>
     </row>
-    <row r="65" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="1"/>
       <c r="E65" s="73"/>
     </row>
-    <row r="66" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="1"/>
       <c r="E66" s="74"/>
     </row>
-    <row r="67" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="75"/>
       <c r="E69" s="75"/>
       <c r="F69" s="75"/>
@@ -15278,7 +15233,7 @@
       <c r="H69" s="75"/>
       <c r="I69" s="75"/>
     </row>
-    <row r="70" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="75"/>
       <c r="E70" s="75"/>
       <c r="F70" s="75"/>
@@ -15286,7 +15241,7 @@
       <c r="H70" s="75"/>
       <c r="I70" s="75"/>
     </row>
-    <row r="71" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="75"/>
       <c r="E71" s="75"/>
       <c r="F71" s="75"/>
@@ -15294,7 +15249,7 @@
       <c r="H71" s="75"/>
       <c r="I71" s="75"/>
     </row>
-    <row r="72" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="75"/>
       <c r="E72" s="75"/>
       <c r="F72" s="75"/>
@@ -15302,59 +15257,59 @@
       <c r="H72" s="75"/>
       <c r="I72" s="75"/>
     </row>
-    <row r="73" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="76"/>
     </row>
-    <row r="79" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="76"/>
     </row>
-    <row r="80" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="76"/>
     </row>
-    <row r="81" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="76"/>
     </row>
-    <row r="82" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="76"/>
     </row>
-    <row r="83" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12" xr:uid="{620909BD-05B7-4260-BB85-4888DFAEE1F3}">
@@ -15380,7 +15335,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:J83"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -15391,7 +15346,7 @@
     <col min="11" max="11" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:10" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:10" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="29" t="s">
         <v>148</v>
       </c>
@@ -15403,7 +15358,7 @@
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
     </row>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -15413,7 +15368,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="3:10" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -15423,7 +15378,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="5" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D5" s="2" t="s">
         <v>88</v>
       </c>
@@ -15431,13 +15386,13 @@
       <c r="F5" s="26"/>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D6" s="33"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="1" t="s">
         <v>89</v>
       </c>
@@ -15447,7 +15402,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="26"/>
     </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="13" t="s">
         <v>91</v>
       </c>
@@ -15457,13 +15412,13 @@
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
     </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="26"/>
       <c r="E9" s="26"/>
       <c r="F9" s="26"/>
       <c r="G9" s="26"/>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="37" t="s">
         <v>93</v>
       </c>
@@ -15471,13 +15426,13 @@
       <c r="F10" s="39"/>
       <c r="G10" s="40"/>
     </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
       <c r="F11" s="26"/>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="13" t="s">
         <v>17</v>
       </c>
@@ -15489,7 +15444,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D13" s="13" t="s">
         <v>18</v>
       </c>
@@ -15502,16 +15457,16 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="F14" s="26"/>
       <c r="G14" s="26"/>
     </row>
-    <row r="16" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D16" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D18" s="1" t="s">
         <v>14</v>
       </c>
@@ -15522,7 +15477,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D19" s="1" t="s">
         <v>15</v>
       </c>
@@ -15533,7 +15488,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D20" s="1" t="s">
         <v>16</v>
       </c>
@@ -15545,7 +15500,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D22" s="1" t="s">
         <v>150</v>
       </c>
@@ -15557,7 +15512,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D23" s="1" t="s">
         <v>154</v>
       </c>
@@ -15568,7 +15523,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="24" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D24" s="1" t="s">
         <v>155</v>
       </c>
@@ -15579,7 +15534,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D25" s="1" t="s">
         <v>156</v>
       </c>
@@ -15591,7 +15546,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D27" s="1" t="s">
         <v>152</v>
       </c>
@@ -15603,7 +15558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D28" s="1" t="s">
         <v>157</v>
       </c>
@@ -15614,7 +15569,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D29" s="1" t="s">
         <v>158</v>
       </c>
@@ -15625,7 +15580,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D30" s="1" t="s">
         <v>156</v>
       </c>
@@ -15637,7 +15592,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D32" s="1" t="s">
         <v>151</v>
       </c>
@@ -15648,7 +15603,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D33" s="1" t="s">
         <v>153</v>
       </c>
@@ -15659,18 +15614,18 @@
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D36" s="2" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="39" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D39" s="80" t="str">
         <f>"Carbon captured from " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Site_EndDate, "d, mmmm, yyyy") &amp; " from environmental plantings"</f>
         <v>Carbon captured from 1 January 2025 to 31, December, 2025 from environmental plantings</v>
       </c>
     </row>
-    <row r="41" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D41" s="21" t="s">
         <v>266</v>
       </c>
@@ -15684,7 +15639,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="42" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D42" s="35"/>
       <c r="E42" s="77"/>
       <c r="F42" s="19"/>
@@ -15693,29 +15648,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D46" s="2" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="48" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D48" s="80" t="str">
         <f>"Gross emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Gross emissions from other activity periods in the production timeframe 1 November 2025 to 31 March 2026</v>
       </c>
     </row>
-    <row r="50" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D50" s="90" t="str" cm="1">
         <f t="array" ref="D50">"There are " &amp; Common_InputFunctions.getOverlappingReportingCycles(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate) &amp; " emissions calculation periods that need to be completed before total product emissions can be determined."</f>
         <v>There are 2 emissions calculation periods that need to be completed before total product emissions can be determined.</v>
       </c>
     </row>
-    <row r="51" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="1" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="53" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D53" s="81" t="s">
         <v>116</v>
       </c>
@@ -15726,7 +15681,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="1" t="str" cm="1">
         <f t="array" ref="D54:D55">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15743,7 +15698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D55" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15759,7 +15714,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="56" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E56" s="77">
         <f>IF(ISBLANK($D56), 0, IF(ISNUMBER(SEARCH("reporting", $D56)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15772,7 +15727,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="57" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E57" s="77">
         <f>IF(ISBLANK($D57), 0, IF(ISNUMBER(SEARCH("reporting", $D57)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15785,7 +15740,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E58" s="77">
         <f>IF(ISBLANK($D58), 0, IF(ISNUMBER(SEARCH("reporting", $D58)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15798,7 +15753,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D59" s="91" t="s">
         <v>129</v>
       </c>
@@ -15814,13 +15769,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D64" s="80" t="str">
         <f>"Carbon removals from environmental plantings for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Carbon removals from environmental plantings for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="66" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D66" s="81" t="s">
         <v>116</v>
       </c>
@@ -15829,7 +15784,7 @@
       </c>
       <c r="F66" s="81"/>
     </row>
-    <row r="67" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D67" s="1" t="str" cm="1">
         <f t="array" ref="D67:D68">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15842,7 +15797,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="68" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D68" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15854,7 +15809,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="69" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E69" s="77">
         <f>IF(ISBLANK($D69), 0, IF(ISNUMBER(SEARCH("reporting", $D69)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15863,7 +15818,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="70" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E70" s="77">
         <f>IF(ISBLANK($D70), 0, IF(ISNUMBER(SEARCH("reporting", $D70)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15872,7 +15827,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="71" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E71" s="77">
         <f>IF(ISBLANK($D71), 0, IF(ISNUMBER(SEARCH("reporting", $D71)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15881,7 +15836,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="72" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D72" s="91" t="s">
         <v>130</v>
       </c>
@@ -15893,13 +15848,13 @@
         <v>128</v>
       </c>
     </row>
-    <row r="75" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D75" s="80" t="str">
         <f>"Net emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Net emissions from other activity periods in the production timeframe 1 November 2025 to 31 March 2026</v>
       </c>
     </row>
-    <row r="77" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D77" s="81" t="s">
         <v>116</v>
       </c>
@@ -15910,7 +15865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D78" s="1" t="str" cm="1">
         <f t="array" ref="D78:D79">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15927,7 +15882,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D79" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15943,7 +15898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E80" s="77">
         <f>IF(ISBLANK($D80), 0, IF(ISNUMBER(SEARCH("reporting", $D80)), E56-$E$69, "Enter value"))</f>
         <v>0</v>
@@ -15956,7 +15911,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E81" s="77">
         <f>IF(ISBLANK($D81), 0, IF(ISNUMBER(SEARCH("reporting", $D81)), E57-$E$70, "Enter value"))</f>
         <v>0</v>
@@ -15969,7 +15924,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E82" s="77">
         <f>IF(ISBLANK($D82), 0, IF(ISNUMBER(SEARCH("reporting", $D82)), E58-$E$71, "Enter value"))</f>
         <v>0</v>
@@ -15982,7 +15937,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D83" s="91" t="s">
         <v>129</v>
       </c>
@@ -16012,7 +15967,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -16021,7 +15976,7 @@
     <col min="11" max="11" width="4.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="A1" s="11" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -16029,8 +15984,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:11" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="1:11" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -16041,7 +15996,7 @@
       <c r="J3" s="30"/>
       <c r="K3" s="30"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D5" s="71" t="s">
         <v>182</v>
       </c>
@@ -16049,10 +16004,10 @@
       <c r="F5" s="71"/>
       <c r="G5" s="71"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="F6" s="17"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="1" t="s">
         <v>178</v>
       </c>
@@ -16061,7 +16016,7 @@
       </c>
       <c r="F7" s="17"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="1" t="s">
         <v>180</v>
       </c>
@@ -16071,7 +16026,7 @@
       </c>
       <c r="F8" s="17"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="1" t="s">
         <v>64</v>
       </c>
@@ -16080,7 +16035,7 @@
         <v>#NAME?</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="1" t="s">
         <v>181</v>
       </c>
@@ -16100,7 +16055,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:M65"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -16113,13 +16068,13 @@
     <col min="14" max="14" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:13" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="11" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:13" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="30"/>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -16132,12 +16087,12 @@
       <c r="L3" s="30"/>
       <c r="M3" s="30"/>
     </row>
-    <row r="5" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D5" s="2" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="81" t="s">
         <v>256</v>
       </c>
@@ -16160,7 +16115,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="1" t="str">
         <f>"Grain yield"</f>
         <v>Grain yield</v>
@@ -16181,7 +16136,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="1" t="str">
         <f>"Grain sold"</f>
         <v>Grain sold</v>
@@ -16202,7 +16157,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="1" t="str">
         <f>"Baled hay/silage produced"</f>
         <v>Baled hay/silage produced</v>
@@ -16223,7 +16178,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="1" t="str">
         <f>"Baled hay/silage sold"</f>
         <v>Baled hay/silage sold</v>
@@ -16244,7 +16199,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="1" t="str">
         <f>"Percent income from grain sold"</f>
         <v>Percent income from grain sold</v>
@@ -16265,7 +16220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D13" s="1" t="str">
         <f>"Percent income from baled hay/silage sold"</f>
         <v>Percent income from baled hay/silage sold</v>
@@ -16286,18 +16241,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J15" s="86">
         <f>SUM(Table_Input_DataQuality_Enterprise[Score])</f>
         <v>60</v>
       </c>
     </row>
-    <row r="16" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D16" s="2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="18" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D18" s="81" t="s">
         <v>256</v>
       </c>
@@ -16320,7 +16275,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="19" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D19" s="1" t="str">
         <f>"Leaching zone"</f>
         <v>Leaching zone</v>
@@ -16341,7 +16296,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D20" s="1" t="str">
         <f>"Elevation"</f>
         <v>Elevation</v>
@@ -16362,7 +16317,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D21" s="1" t="str">
         <f>"Average temperature for reporting period"</f>
         <v>Average temperature for reporting period</v>
@@ -16383,7 +16338,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D22" s="1" t="str">
         <f>"Total rainfall for reporting period"</f>
         <v>Total rainfall for reporting period</v>
@@ -16404,7 +16359,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D23" s="1" t="str">
         <f>"Potential evapotranspiration for reporting period"</f>
         <v>Potential evapotranspiration for reporting period</v>
@@ -16425,7 +16380,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D24" s="1" t="str">
         <f>"Number of frost days for reporting period"</f>
         <v>Number of frost days for reporting period</v>
@@ -16446,18 +16401,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J26" s="86">
         <f>SUM(Table_Input_DataQuality_Site[Score])</f>
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D27" s="2" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="29" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D29" s="81" t="s">
         <v>256</v>
       </c>
@@ -16480,7 +16435,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="30" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D30" s="1" t="str">
         <f>"Crop type"</f>
         <v>Crop type</v>
@@ -16501,7 +16456,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D31" s="1" t="str">
         <f>"Irrigation method"</f>
         <v>Irrigation method</v>
@@ -16522,7 +16477,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D32" s="1" t="str">
         <f>"Area under cropping"</f>
         <v>Area under cropping</v>
@@ -16543,7 +16498,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D33" s="1" t="str">
         <f>"Residue management"</f>
         <v>Residue management</v>
@@ -16564,18 +16519,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J35" s="86">
         <f>SUM(Table_Input_DataQuality_PastureManagement[Score])</f>
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D36" s="2" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="38" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D38" s="81" t="s">
         <v>256</v>
       </c>
@@ -16598,7 +16553,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="39" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D39" s="1" t="str">
         <f>"Branded inorganic fertiliser applications"</f>
         <v>Branded inorganic fertiliser applications</v>
@@ -16619,7 +16574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D40" s="1" t="str">
         <f>"Custom inorganic fertiliser blend applications"</f>
         <v>Custom inorganic fertiliser blend applications</v>
@@ -16640,7 +16595,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D41" s="1" t="str">
         <f>"Lime applications"</f>
         <v>Lime applications</v>
@@ -16661,7 +16616,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D42" s="1" t="str">
         <f>"Organic fertiliser applications"</f>
         <v>Organic fertiliser applications</v>
@@ -16682,18 +16637,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J44" s="86">
         <f>SUM(Table_Input_DataQuality_FertiliserApplications[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D45" s="2" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D47" s="81" t="s">
         <v>256</v>
       </c>
@@ -16716,7 +16671,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="1" t="str">
         <f>"Fuel purchases"</f>
         <v>Fuel purchases</v>
@@ -16737,7 +16692,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D49" s="1" t="str">
         <f>"Fuel consumption"</f>
         <v>Fuel consumption</v>
@@ -16758,7 +16713,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D50" s="1" t="str">
         <f>"Electricity consumption"</f>
         <v>Electricity consumption</v>
@@ -16779,7 +16734,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="1" t="str">
         <f>"Electricity generation"</f>
         <v>Electricity generation</v>
@@ -16800,18 +16755,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J53" s="86">
         <f>SUM(Table_Input_DataQuality_FuelElectricity[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="55" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D55" s="2" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D57" s="81" t="s">
         <v>256</v>
       </c>
@@ -16834,7 +16789,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="58" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D58" s="1" t="str">
         <f>"Farm input purchases"</f>
         <v>Farm input purchases</v>
@@ -16855,7 +16810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D59" s="1" t="str">
         <f>"Inbound freight use"</f>
         <v>Inbound freight use</v>
@@ -16876,7 +16831,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D60" s="1" t="str">
         <f>"Outbound freight use"</f>
         <v>Outbound freight use</v>
@@ -16897,7 +16852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D61" s="1" t="str">
         <f>"Solid waste generation and treatment"</f>
         <v>Solid waste generation and treatment</v>
@@ -16918,13 +16873,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J63" s="86">
         <f>SUM(Table_Input_DataQuality_FarmInputsFreightWaste[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="65" spans="4:5" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:5" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D65" s="88" t="s">
         <v>264</v>
       </c>
@@ -16963,7 +16918,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="23" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="23" customWidth="1"/>
@@ -16996,10 +16951,10 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -17026,11 +16981,11 @@
       <c r="V3" s="25"/>
       <c r="W3" s="25"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="26"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="2" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -17038,7 +16993,7 @@
       </c>
       <c r="BM5" s="26"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="83" t="s">
         <v>2</v>
       </c>
@@ -17052,7 +17007,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="84" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -17070,7 +17025,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -17088,7 +17043,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="21" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17103,7 +17058,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="21" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17118,7 +17073,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="21" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17134,7 +17089,7 @@
       </c>
       <c r="BM11" s="26"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="21" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17150,7 +17105,7 @@
       </c>
       <c r="BM12" s="26"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="21" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17165,7 +17120,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="21" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -17180,129 +17135,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="2" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="18" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="21" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="21" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="21" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="21" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="21" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="21" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="21" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="21" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="21" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="21" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="2" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="18" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="21" t="s">
         <v>26</v>
@@ -17311,7 +17266,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="21" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17322,7 +17277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="21" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17333,7 +17288,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="21" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17344,7 +17299,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="21" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17355,7 +17310,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="21" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17366,7 +17321,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="21" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17377,7 +17332,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="21" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -17388,24 +17343,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="2" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="18" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="21" t="s">
         <v>26</v>
@@ -17423,7 +17378,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="21" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17446,7 +17401,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="21" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17469,7 +17424,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="21" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17492,7 +17447,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="21" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17515,7 +17470,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="21" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17538,7 +17493,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="21" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17561,7 +17516,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="21" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17584,49 +17539,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="2" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="18" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="27" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="27" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="27" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="21" t="s">
         <v>32</v>
@@ -17635,7 +17590,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="21" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17646,7 +17601,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="21" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17657,7 +17612,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="21" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17668,7 +17623,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="21" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17679,7 +17634,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="21" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17690,7 +17645,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="21" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17701,7 +17656,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="21" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17712,7 +17667,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="21" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17723,7 +17678,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="21" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17734,7 +17689,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="21" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17745,7 +17700,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="21" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17756,7 +17711,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="21" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17767,7 +17722,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="21" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17778,7 +17733,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="21" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17789,64 +17744,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="2" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="18" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="27" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="27" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="27" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="27" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="27" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="21" t="s">
         <v>32</v>
@@ -17898,7 +17853,7 @@
       </c>
       <c r="T89" s="21"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="21" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17966,7 +17921,7 @@
       </c>
       <c r="T90" s="21"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="21" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18034,7 +17989,7 @@
       </c>
       <c r="T91" s="21"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="21" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18102,7 +18057,7 @@
       </c>
       <c r="T92" s="21"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="21" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18170,7 +18125,7 @@
       </c>
       <c r="T93" s="21"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="21" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18238,7 +18193,7 @@
       </c>
       <c r="T94" s="21"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="21" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18306,7 +18261,7 @@
       </c>
       <c r="T95" s="21"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="21" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18374,7 +18329,7 @@
       </c>
       <c r="T96" s="21"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="21" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -18442,66 +18397,66 @@
       </c>
       <c r="T97" s="21"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="10" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="10" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="10" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="10" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="10"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="2" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="18" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="27" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="21" t="s">
         <v>49</v>
@@ -18516,7 +18471,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="21" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18535,7 +18490,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="21" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18554,7 +18509,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="21" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18573,13 +18528,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="2" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -18587,7 +18542,7 @@
       </c>
       <c r="BN115" s="23"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="18" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -18595,7 +18550,7 @@
       </c>
       <c r="BN116" s="23"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="27" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -18603,11 +18558,11 @@
       </c>
       <c r="BN117" s="23"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="23"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="21" t="s">
         <v>52</v>
@@ -18623,7 +18578,7 @@
       </c>
       <c r="BN119" s="23"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="21" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18643,7 +18598,7 @@
       </c>
       <c r="BN120" s="23"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="21" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18663,31 +18618,31 @@
       </c>
       <c r="BN121" s="23"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="23"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="2" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="18" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="21" t="s">
         <v>54</v>
@@ -18696,7 +18651,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="21" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18707,7 +18662,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="21" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18718,13 +18673,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="2" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -18732,7 +18687,7 @@
       </c>
       <c r="E132" s="9"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="18" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -18740,7 +18695,7 @@
       </c>
       <c r="E133" s="9"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>56</v>
@@ -18749,7 +18704,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18760,7 +18715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18771,10 +18726,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="23"/>
       <c r="BO138" s="23"/>
@@ -18789,7 +18744,7 @@
       <c r="BX138" s="23"/>
       <c r="BY138" s="23"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="2" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -18808,7 +18763,7 @@
       <c r="BX139" s="23"/>
       <c r="BY139" s="23"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="18" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -18827,7 +18782,7 @@
       <c r="BX140" s="23"/>
       <c r="BY140" s="23"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="27" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -18835,7 +18790,7 @@
       </c>
       <c r="BN141" s="23"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="21" t="s">
         <v>58</v>
@@ -18845,7 +18800,7 @@
       </c>
       <c r="BN142" s="23"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="21" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18857,7 +18812,7 @@
       </c>
       <c r="BN143" s="23"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18869,7 +18824,7 @@
       </c>
       <c r="BN144" s="23"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18881,7 +18836,7 @@
       </c>
       <c r="BN145" s="23"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18893,7 +18848,7 @@
       </c>
       <c r="BN146" s="23"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18905,15 +18860,15 @@
       </c>
       <c r="BN147" s="23"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="23"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="23"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="2" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -18921,7 +18876,7 @@
       </c>
       <c r="BN150" s="23"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="18" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -18929,11 +18884,11 @@
       </c>
       <c r="BN151" s="23"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="23"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="21" t="s">
         <v>59</v>
@@ -18953,7 +18908,7 @@
       <c r="BL153" s="26"/>
       <c r="BM153" s="26"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="21" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18975,7 +18930,7 @@
       <c r="BL154" s="26"/>
       <c r="BM154" s="26"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="21" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18997,7 +18952,7 @@
       <c r="BL155" s="26"/>
       <c r="BM155" s="26"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="21" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19008,7 +18963,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="21" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19019,7 +18974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="21" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -19030,34 +18985,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="2" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="9"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="18" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="9"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="18" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="9"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="9" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -19066,17 +19021,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="23"/>
       <c r="BO165" s="23"/>
       <c r="BP165" s="23"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="23"/>
       <c r="BO166" s="23"/>
       <c r="BP166" s="23"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="2" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -19085,7 +19040,7 @@
       <c r="BO167" s="23"/>
       <c r="BP167" s="23"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="18" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -19094,7 +19049,7 @@
       <c r="BO168" s="23"/>
       <c r="BP168" s="23"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="18" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -19103,7 +19058,7 @@
       <c r="BO169" s="23"/>
       <c r="BP169" s="23"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -19115,17 +19070,17 @@
       <c r="BO170" s="23"/>
       <c r="BP170" s="23"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="23"/>
       <c r="BO171" s="23"/>
       <c r="BP171" s="23"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="23"/>
       <c r="BO172" s="23"/>
       <c r="BP172" s="23"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="2" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -19134,7 +19089,7 @@
       <c r="BO173" s="23"/>
       <c r="BP173" s="23"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="18" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -19143,7 +19098,7 @@
       <c r="BO174" s="23"/>
       <c r="BP174" s="23"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -19156,17 +19111,17 @@
       <c r="BO175" s="23"/>
       <c r="BP175" s="23"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="23"/>
       <c r="BO176" s="23"/>
       <c r="BP176" s="23"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="23"/>
       <c r="BO177" s="23"/>
       <c r="BP177" s="23"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="2" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -19175,7 +19130,7 @@
       <c r="BO178" s="23"/>
       <c r="BP178" s="23"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="18" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -19184,39 +19139,39 @@
       <c r="BO179" s="23"/>
       <c r="BP179" s="23"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="10" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="27" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="27" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="27" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="27" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="27" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="21" t="s">
         <v>61</v>
       </c>
@@ -19233,7 +19188,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="21" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -19255,7 +19210,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="21" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -19277,7 +19232,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="21" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -19299,7 +19254,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="21" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -19321,7 +19276,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="21" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -19343,7 +19298,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="21" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -19365,7 +19320,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="21" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -19387,7 +19342,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="21" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -19409,7 +19364,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="21" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -19431,7 +19386,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="21" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -19453,7 +19408,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="21" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -19475,7 +19430,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="21" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -19497,7 +19452,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="21" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -19519,31 +19474,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="2" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="18" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="27" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="10" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="21" t="s">
         <v>32</v>
       </c>
@@ -19551,7 +19506,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="21" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -19561,7 +19516,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -19571,13 +19526,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="21" t="s">
         <v>67</v>
       </c>
@@ -19585,7 +19540,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="21" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -19595,7 +19550,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -19605,7 +19560,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -19615,7 +19570,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -19625,7 +19580,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -19635,7 +19590,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -19645,7 +19600,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -19655,7 +19610,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -19665,7 +19620,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -19675,7 +19630,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -19685,7 +19640,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -19695,7 +19650,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -19705,25 +19660,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="2" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="18" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="27" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="21" t="s">
         <v>69</v>
       </c>
@@ -19773,7 +19728,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="21" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19839,7 +19794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19905,7 +19860,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19971,7 +19926,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -20037,7 +19992,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -20103,7 +20058,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20169,7 +20124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20235,7 +20190,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20301,7 +20256,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20367,7 +20322,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20433,7 +20388,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20499,7 +20454,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20565,7 +20520,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20631,7 +20586,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20697,7 +20652,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20763,7 +20718,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20829,7 +20784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20895,7 +20850,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20961,7 +20916,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -21027,31 +20982,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="2" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="18" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="10" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="21" t="s">
         <v>85</v>
       </c>
@@ -21059,7 +21014,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="258" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="21" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -21069,7 +21024,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -21079,17 +21034,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:66" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:66" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="2" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="264" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="265" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="21" t="s">
         <v>234</v>
       </c>
@@ -21105,7 +21060,7 @@
       <c r="V265" s="1"/>
       <c r="BN265" s="23"/>
     </row>
-    <row r="266" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="21" t="s">
         <v>235</v>
       </c>
@@ -21121,7 +21076,7 @@
       <c r="V266" s="1"/>
       <c r="BN266" s="23"/>
     </row>
-    <row r="267" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="21" t="s">
         <v>236</v>
       </c>
@@ -21137,7 +21092,7 @@
       <c r="V267" s="1"/>
       <c r="BN267" s="23"/>
     </row>
-    <row r="268" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="21" t="s">
         <v>237</v>
       </c>
@@ -21153,7 +21108,7 @@
       <c r="V268" s="1"/>
       <c r="BN268" s="23"/>
     </row>
-    <row r="269" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="21" t="s">
         <v>238</v>
       </c>
@@ -21169,7 +21124,7 @@
       <c r="V269" s="1"/>
       <c r="BN269" s="23"/>
     </row>
-    <row r="270" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="21" t="s">
         <v>239</v>
       </c>
@@ -21185,12 +21140,12 @@
       <c r="V270" s="1"/>
       <c r="BN270" s="23"/>
     </row>
-    <row r="273" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="274" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="21" t="s">
         <v>234</v>
       </c>
@@ -21206,7 +21161,7 @@
       <c r="V274" s="1"/>
       <c r="BN274" s="23"/>
     </row>
-    <row r="275" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="21" t="s">
         <v>240</v>
       </c>
@@ -21222,7 +21177,7 @@
       <c r="V275" s="1"/>
       <c r="BN275" s="23"/>
     </row>
-    <row r="276" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="21" t="s">
         <v>241</v>
       </c>
@@ -21238,7 +21193,7 @@
       <c r="V276" s="1"/>
       <c r="BN276" s="23"/>
     </row>
-    <row r="277" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="21" t="s">
         <v>242</v>
       </c>
@@ -21254,7 +21209,7 @@
       <c r="V277" s="1"/>
       <c r="BN277" s="23"/>
     </row>
-    <row r="278" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="21" t="s">
         <v>243</v>
       </c>
@@ -21270,7 +21225,7 @@
       <c r="V278" s="1"/>
       <c r="BN278" s="23"/>
     </row>
-    <row r="279" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="21" t="s">
         <v>244</v>
       </c>
@@ -21286,12 +21241,12 @@
       <c r="V279" s="1"/>
       <c r="BN279" s="23"/>
     </row>
-    <row r="282" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="283" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="21" t="s">
         <v>234</v>
       </c>
@@ -21307,7 +21262,7 @@
       <c r="V283" s="1"/>
       <c r="BN283" s="23"/>
     </row>
-    <row r="284" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="21" t="s">
         <v>245</v>
       </c>
@@ -21323,7 +21278,7 @@
       <c r="V284" s="1"/>
       <c r="BN284" s="23"/>
     </row>
-    <row r="285" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="21" t="s">
         <v>246</v>
       </c>
@@ -21339,7 +21294,7 @@
       <c r="V285" s="1"/>
       <c r="BN285" s="23"/>
     </row>
-    <row r="286" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="21" t="s">
         <v>247</v>
       </c>
@@ -21355,7 +21310,7 @@
       <c r="V286" s="1"/>
       <c r="BN286" s="23"/>
     </row>
-    <row r="287" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="21" t="s">
         <v>248</v>
       </c>
@@ -21371,7 +21326,7 @@
       <c r="V287" s="1"/>
       <c r="BN287" s="23"/>
     </row>
-    <row r="288" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="21" t="s">
         <v>249</v>
       </c>
@@ -21387,12 +21342,12 @@
       <c r="V288" s="1"/>
       <c r="BN288" s="23"/>
     </row>
-    <row r="291" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="292" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="21" t="s">
         <v>234</v>
       </c>
@@ -21408,7 +21363,7 @@
       <c r="V292" s="1"/>
       <c r="BN292" s="23"/>
     </row>
-    <row r="293" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="21" t="s">
         <v>250</v>
       </c>
@@ -21424,7 +21379,7 @@
       <c r="V293" s="1"/>
       <c r="BN293" s="23"/>
     </row>
-    <row r="294" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="21" t="s">
         <v>251</v>
       </c>
@@ -21440,7 +21395,7 @@
       <c r="V294" s="1"/>
       <c r="BN294" s="23"/>
     </row>
-    <row r="295" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="21" t="s">
         <v>252</v>
       </c>
@@ -21456,7 +21411,7 @@
       <c r="V295" s="1"/>
       <c r="BN295" s="23"/>
     </row>
-    <row r="296" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="21" t="s">
         <v>253</v>
       </c>
@@ -21472,7 +21427,7 @@
       <c r="V296" s="1"/>
       <c r="BN296" s="23"/>
     </row>
-    <row r="297" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="21" t="s">
         <v>254</v>
       </c>
